--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486426_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486426_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8133</v>
+        <v>5.137</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2785</v>
+        <v>4.7255</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.4115</v>
       </c>
       <c r="G2" t="n">
         <v>7.0935</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3103</v>
+        <v>-0.9866</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9589</v>
+        <v>-0.5119</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3514</v>
+        <v>-0.4747</v>
       </c>
       <c r="V2" t="n">
         <v>3.8153</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3397</v>
+        <v>2.0448</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7998</v>
+        <v>3.1351</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4601</v>
+        <v>-1.0902</v>
       </c>
       <c r="G3" t="n">
         <v>2.572</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3324</v>
+        <v>-0.6273</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.3497</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6475</v>
+        <v>-0.2776</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3349</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3306</v>
+        <v>1.7892</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6818</v>
+        <v>2.017</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3512</v>
+        <v>-0.2279</v>
       </c>
       <c r="G4" t="n">
         <v>2.6828</v>
@@ -766,13 +766,13 @@
         <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0174</v>
+        <v>-0.5588</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.548</v>
+        <v>-0.2127</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4694</v>
+        <v>-0.3461</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3349</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2523</v>
+        <v>-0.4444</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9469</v>
+        <v>-0.7788</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1993</v>
+        <v>0.3343</v>
       </c>
       <c r="G5" t="n">
-        <v>2.058</v>
+        <v>1.3927</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4476</v>
+        <v>-0.0186</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6104000000000001</v>
+        <v>1.4112</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1506</v>
+        <v>1.6878</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8828</v>
+        <v>0.7482</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2677</v>
+        <v>0.9395</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0926</v>
+        <v>-0.2951</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4353</v>
+        <v>-0.7668</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3426</v>
+        <v>0.4717</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q5" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>0.464</v>
+        <v>-0.5245</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.4867</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4724</v>
+        <v>-0.0379</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8346</v>
+        <v>-1.0951</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.9141</v>
+        <v>0.1952</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9205</v>
+        <v>-1.2903</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6936</v>
+        <v>-0.4451</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0681</v>
+        <v>-1.0587</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3745</v>
+        <v>0.6136</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2461</v>
+        <v>2.058</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0767</v>
+        <v>1.4476</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3228</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7673</v>
+        <v>2.1506</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3618</v>
+        <v>1.8828</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1292</v>
+        <v>0.2677</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5213</v>
+        <v>-0.0926</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7149</v>
+        <v>-0.4353</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1936</v>
+        <v>0.3426</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2349</v>
+        <v>-0.2334</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0791</v>
+        <v>-0.1202</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1557</v>
+        <v>-0.1133</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3045</v>
+        <v>-1.8346</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7395</v>
+        <v>-0.9141</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.9205</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>J. ARIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0879</v>
+        <v>-1.1103</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.114</v>
+        <v>-1.3975</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0261</v>
+        <v>0.2872</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3927</v>
+        <v>0.3797</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0186</v>
+        <v>-0.3956</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4112</v>
+        <v>0.7753</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6878</v>
+        <v>0.1695</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7482</v>
+        <v>0.0547</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9395</v>
+        <v>0.1147</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2951</v>
+        <v>0.2102</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7668</v>
+        <v>-0.4504</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4717</v>
+        <v>0.6606</v>
       </c>
       <c r="P7" t="n">
         <v>-0.2175</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.168</v>
+        <v>-1.0773</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.822</v>
+        <v>-0.4795</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3461</v>
+        <v>-0.5979</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0951</v>
+        <v>-0.1952</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2903</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ARIAS GONZALEZ</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.172</v>
+        <v>-1.526</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3975</v>
+        <v>-0.4478</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2255</v>
+        <v>-1.0782</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3797</v>
+        <v>-0.8484</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3956</v>
+        <v>-0.14</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7753</v>
+        <v>-0.7084</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1695</v>
+        <v>0.7335</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0547</v>
+        <v>0.657</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1147</v>
+        <v>0.0765</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2102</v>
+        <v>-1.5819</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4504</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6606</v>
+        <v>-0.7849</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2175</v>
+        <v>-0.435</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.139</v>
+        <v>0.3224</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4795</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6595</v>
+        <v>0.4161</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1952</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1952</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3604</v>
+        <v>-1.5992</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5595</v>
+        <v>-1.8504</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8008</v>
+        <v>0.2512</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8484</v>
+        <v>0.2461</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.14</v>
+        <v>-1.0767</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7084</v>
+        <v>1.3228</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7335</v>
+        <v>0.7673</v>
       </c>
       <c r="K9" t="n">
-        <v>0.657</v>
+        <v>-0.3618</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0765</v>
+        <v>1.1292</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5819</v>
+        <v>-0.5213</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.7149</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7849</v>
+        <v>0.1936</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.435</v>
+        <v>-0.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>0.488</v>
+        <v>0.3293</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2055</v>
+        <v>0.2968</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6935</v>
+        <v>0.0324</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.3045</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X9" t="n">
         <v>-0.5649999999999999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1792</v>
+        <v>-2.8382</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6813</v>
+        <v>-0.101</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8605</v>
+        <v>-2.7372</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2327</v>
@@ -1234,13 +1234,13 @@
         <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3358</v>
+        <v>-0.3233</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8051</v>
+        <v>0.0228</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4694</v>
+        <v>-0.3461</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4997</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3654</v>
+        <v>-3.1304</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3665</v>
+        <v>-3.2547</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001</v>
+        <v>0.1243</v>
       </c>
       <c r="G11" t="n">
         <v>0.33</v>
@@ -1312,13 +1312,13 @@
         <v>1.9576</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0859</v>
+        <v>-0.8508</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6165</v>
+        <v>-0.5047</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4694</v>
+        <v>-0.3461</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3045</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.122600000000001</v>
+        <v>-2.122600000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9889000000000006</v>
+        <v>0.9887000000000001</v>
       </c>
       <c r="F12" t="n">
         <v>-3.1114</v>
@@ -1393,10 +1393,10 @@
         <v>-4.5303</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.4396</v>
+        <v>-2.4395</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.0911</v>
+        <v>-2.0912</v>
       </c>
       <c r="V12" t="n">
         <v>-4.653099999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.0059</v>
+        <v>7.4336</v>
       </c>
       <c r="E13" t="n">
-        <v>6.782</v>
+        <v>7.1173</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2239</v>
+        <v>0.3164</v>
       </c>
       <c r="G13" t="n">
         <v>2.5466</v>
@@ -1468,13 +1468,13 @@
         <v>3.0451</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3597</v>
+        <v>0.7874</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0601</v>
+        <v>0.3954</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2996</v>
+        <v>0.392</v>
       </c>
       <c r="V13" t="n">
         <v>3.2296</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2608</v>
+        <v>2.6355</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8766</v>
+        <v>2.0768</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3842</v>
+        <v>0.5587</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2863</v>
+        <v>0.2309</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.5087</v>
+        <v>0.0333</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2224</v>
+        <v>0.1976</v>
       </c>
       <c r="J14" t="n">
-        <v>1.149</v>
+        <v>1.5012</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.6448</v>
+        <v>0.2007</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7938</v>
+        <v>1.3005</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4353</v>
+        <v>-1.2703</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8639</v>
+        <v>-0.1674</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5714</v>
+        <v>-1.1029</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2175</v>
+        <v>1.7401</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3926</v>
+        <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1854</v>
+        <v>0.6645</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2077</v>
+        <v>0.5756</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0224</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1442</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5508</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1885</v>
+        <v>1.6017</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6298</v>
+        <v>1.0943</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5587</v>
+        <v>0.5075</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2309</v>
+        <v>-0.2863</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0333</v>
+        <v>-2.5087</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1976</v>
+        <v>2.2224</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5012</v>
+        <v>1.149</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2007</v>
+        <v>-1.6448</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3005</v>
+        <v>2.7938</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2703</v>
+        <v>-1.4353</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1674</v>
+        <v>-0.8639</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1029</v>
+        <v>-0.5714</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7401</v>
+        <v>0.2175</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2175</v>
+        <v>0.5264</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1286</v>
+        <v>0.4254</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1009</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.1442</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5508</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4917</v>
+        <v>1.5418</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9617</v>
+        <v>1.0735</v>
       </c>
       <c r="F16" t="n">
-        <v>0.53</v>
+        <v>0.4683</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0267</v>
@@ -1702,13 +1702,13 @@
         <v>2.6101</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3014</v>
+        <v>0.3515</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0601</v>
+        <v>0.1719</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2413</v>
+        <v>0.1796</v>
       </c>
       <c r="V16" t="n">
         <v>1.8695</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9243</v>
+        <v>0.7008</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5578</v>
+        <v>0.3343</v>
       </c>
       <c r="F17" t="n">
         <v>0.3665</v>
@@ -1780,10 +1780,10 @@
         <v>0.2175</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5396</v>
+        <v>0.316</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5396</v>
+        <v>0.316</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1902</v>
+        <v>-0.0949</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8232</v>
+        <v>1.5997</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.633</v>
+        <v>-1.6946</v>
       </c>
       <c r="G19" t="n">
         <v>-0.442</v>
@@ -1936,13 +1936,13 @@
         <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.2818</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2656</v>
+        <v>0.0421</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3014</v>
+        <v>0.2397</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3698</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2976</v>
+        <v>-1.1858</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4325</v>
+        <v>1.5443</v>
       </c>
       <c r="F20" t="n">
         <v>-2.7301</v>
@@ -2014,10 +2014,10 @@
         <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2055</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.548</v>
+        <v>-0.4362</v>
       </c>
       <c r="U20" t="n">
         <v>0.3425</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3189</v>
+        <v>-2.1012</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4296</v>
+        <v>-2.2119</v>
       </c>
       <c r="F21" t="n">
         <v>0.1107</v>
@@ -2092,10 +2092,10 @@
         <v>1.7401</v>
       </c>
       <c r="S21" t="n">
-        <v>1.9371</v>
+        <v>1.1548</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5502</v>
+        <v>0.7679</v>
       </c>
       <c r="U21" t="n">
         <v>0.3869</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1398</v>
+        <v>-3.581</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.437</v>
+        <v>-3.8782</v>
       </c>
       <c r="F22" t="n">
         <v>0.2972</v>
@@ -2170,10 +2170,10 @@
         <v>2.1751</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.024</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.411</v>
+        <v>0.1478</v>
       </c>
       <c r="U22" t="n">
         <v>0.3869</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.5385</v>
+        <v>-5.1839</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.9376</v>
+        <v>-5.4905</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3991</v>
+        <v>0.3066</v>
       </c>
       <c r="G23" t="n">
         <v>-4.9374</v>
@@ -2248,13 +2248,13 @@
         <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.2911</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.822</v>
+        <v>-0.3749</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1763</v>
+        <v>0.0838</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3904</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.1226</v>
+        <v>2.122599999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>3.1112</v>
+        <v>3.111400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9886999999999999</v>
+        <v>-0.9887000000000006</v>
       </c>
       <c r="G24" t="n">
         <v>-14.6736</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0633</v>
+        <v>-1.063300000000001</v>
       </c>
       <c r="I24" t="n">
         <v>-13.6104</v>
@@ -2326,13 +2326,13 @@
         <v>21.7508</v>
       </c>
       <c r="S24" t="n">
-        <v>4.5305</v>
+        <v>4.530399999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>2.091</v>
+        <v>2.0911</v>
       </c>
       <c r="U24" t="n">
-        <v>2.4393</v>
+        <v>2.4391</v>
       </c>
       <c r="V24" t="n">
         <v>4.653</v>
